--- a/Exam/0503-finalreview.xlsx
+++ b/Exam/0503-finalreview.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\#MS\SP25\EAS5450-Eng_Entrepreneurship\Exam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C95AC40B-B455-44F2-9FE2-EF798E033BE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70711234-3F21-4D8F-9804-DF96B50D4979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36600" yWindow="0" windowWidth="14914" windowHeight="11709" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16371" yWindow="0" windowWidth="16629" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="review todo" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="55">
   <si>
     <t>Date</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -212,6 +212,13 @@
   </si>
   <si>
     <t>19.7/25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>√</t>
+  </si>
+  <si>
+    <t>√</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -264,12 +271,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -282,20 +286,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="9">
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -310,6 +305,12 @@
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -337,13 +338,13 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E93CC7B0-365E-4121-9474-8BD0C8DC1815}" name="表3" displayName="表3" ref="A1:G29" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
   <autoFilter ref="A1:G29" xr:uid="{E93CC7B0-365E-4121-9474-8BD0C8DC1815}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{9C735D13-B4C4-4D39-9802-23093CA7D833}" name="Date" dataDxfId="0"/>
-    <tableColumn id="8" xr3:uid="{9F5B857F-1393-4EBF-B15A-00D2D0F4F783}" name="Done?" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{B8B24FB8-62C2-4797-9FD7-8C4978BC8576}" name="Topic" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{8BA8C7C2-AE19-455E-8410-EB0EA4CCC7F0}" name="Key Concepts" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{B6843B60-E96C-45B6-B7B5-930471E20B54}" name="comment" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{6079A1E1-7F11-447F-9326-D5FADEBD3B01}" name="Essay " dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{9084F296-5B4D-4992-BEFB-446CBE48B135}" name="Quiz" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{9C735D13-B4C4-4D39-9802-23093CA7D833}" name="Date" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{9F5B857F-1393-4EBF-B15A-00D2D0F4F783}" name="Done?" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{B8B24FB8-62C2-4797-9FD7-8C4978BC8576}" name="Topic" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{8BA8C7C2-AE19-455E-8410-EB0EA4CCC7F0}" name="Key Concepts" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{B6843B60-E96C-45B6-B7B5-930471E20B54}" name="comment" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{6079A1E1-7F11-447F-9326-D5FADEBD3B01}" name="Essay " dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{9084F296-5B4D-4992-BEFB-446CBE48B135}" name="Quiz" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -615,15 +616,15 @@
   <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.2109375" style="4" customWidth="1"/>
+    <col min="1" max="1" width="6.2109375" style="3" customWidth="1"/>
     <col min="2" max="2" width="6.2109375" customWidth="1"/>
     <col min="3" max="3" width="22.2109375" customWidth="1"/>
     <col min="4" max="5" width="28" customWidth="1"/>
-    <col min="6" max="7" width="9.140625" style="4"/>
+    <col min="6" max="7" width="9.140625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -638,464 +639,478 @@
       <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="28.3" x14ac:dyDescent="0.35">
-      <c r="A2" s="7">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="6">
+      <c r="E2" s="2"/>
+      <c r="F2" s="5">
         <v>8</v>
       </c>
-      <c r="G2" s="6"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3" spans="1:7" ht="28.3" x14ac:dyDescent="0.35">
-      <c r="A3" s="6">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3" t="s">
+      <c r="B3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6">
+      <c r="E3" s="2"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5">
         <v>6.5</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="42.45" x14ac:dyDescent="0.35">
-      <c r="A4" s="7">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="3" t="s">
+      <c r="B4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="D4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="6">
-        <v>10</v>
-      </c>
-      <c r="G4" s="6"/>
+      <c r="F4" s="5">
+        <v>10</v>
+      </c>
+      <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7" ht="28.3" x14ac:dyDescent="0.35">
-      <c r="A5" s="6">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3" t="s">
+      <c r="B5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6">
+      <c r="E5" s="2"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="28.3" x14ac:dyDescent="0.35">
-      <c r="A6" s="7">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="3" t="s">
+      <c r="B6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="6">
+      <c r="E6" s="2"/>
+      <c r="F6" s="5">
         <v>8</v>
       </c>
-      <c r="G6" s="6"/>
+      <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7" ht="28.3" x14ac:dyDescent="0.35">
-      <c r="A7" s="6">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3" t="s">
+      <c r="B7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6">
+      <c r="E7" s="2"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5">
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="28.3" x14ac:dyDescent="0.35">
-      <c r="A8" s="7">
+      <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="3" t="s">
+      <c r="B8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="6">
-        <v>10</v>
-      </c>
-      <c r="G8" s="6"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="5">
+        <v>10</v>
+      </c>
+      <c r="G8" s="5"/>
     </row>
     <row r="9" spans="1:7" ht="28.3" x14ac:dyDescent="0.35">
-      <c r="A9" s="6">
+      <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3" t="s">
+      <c r="B9" s="2"/>
+      <c r="C9" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6">
+      <c r="E9" s="2"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="28.3" x14ac:dyDescent="0.35">
-      <c r="A10" s="7">
+      <c r="A10" s="5">
         <v>9</v>
       </c>
       <c r="B10" s="2"/>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="6">
+      <c r="E10" s="2"/>
+      <c r="F10" s="5">
         <v>8.75</v>
       </c>
-      <c r="G10" s="6"/>
+      <c r="G10" s="5"/>
     </row>
     <row r="11" spans="1:7" ht="28.3" x14ac:dyDescent="0.35">
-      <c r="A11" s="6">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3" t="s">
+      <c r="A11" s="5">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6">
+      <c r="E11" s="2"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5">
         <v>7.5</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="28.3" x14ac:dyDescent="0.35">
-      <c r="A12" s="7">
+      <c r="A12" s="5">
         <v>11</v>
       </c>
       <c r="B12" s="2"/>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="6">
-        <v>10</v>
-      </c>
-      <c r="G12" s="6"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="5">
+        <v>10</v>
+      </c>
+      <c r="G12" s="5"/>
     </row>
     <row r="13" spans="1:7" ht="28.3" x14ac:dyDescent="0.35">
-      <c r="A13" s="6">
+      <c r="A13" s="5">
         <v>12</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3" t="s">
+      <c r="B13" s="2"/>
+      <c r="C13" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6">
+      <c r="E13" s="2"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5">
         <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="28.3" x14ac:dyDescent="0.35">
-      <c r="A14" s="7">
+      <c r="A14" s="5">
         <v>13</v>
       </c>
       <c r="B14" s="2"/>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="6">
+      <c r="E14" s="2"/>
+      <c r="F14" s="5">
         <v>8</v>
       </c>
-      <c r="G14" s="6"/>
+      <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="6">
+      <c r="A15" s="5">
         <v>14</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3" t="s">
+      <c r="B15" s="2"/>
+      <c r="C15" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6">
+      <c r="E15" s="2"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5">
         <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="28.3" x14ac:dyDescent="0.35">
-      <c r="A16" s="7">
+      <c r="A16" s="5">
         <v>15</v>
       </c>
       <c r="B16" s="2"/>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="6">
+      <c r="E16" s="2"/>
+      <c r="F16" s="5">
         <v>9</v>
       </c>
-      <c r="G16" s="6"/>
+      <c r="G16" s="5"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" s="6">
+      <c r="A17" s="5">
         <v>16</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3" t="s">
+      <c r="B17" s="2"/>
+      <c r="C17" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="6">
-        <v>10</v>
-      </c>
-      <c r="G17" s="6"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="5">
+        <v>10</v>
+      </c>
+      <c r="G17" s="5"/>
     </row>
     <row r="18" spans="1:7" ht="28.3" x14ac:dyDescent="0.35">
-      <c r="A18" s="7">
+      <c r="A18" s="5">
         <v>17</v>
       </c>
       <c r="B18" s="2"/>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="6">
-        <v>10</v>
-      </c>
-      <c r="G18" s="6"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="5">
+        <v>10</v>
+      </c>
+      <c r="G18" s="5"/>
     </row>
     <row r="19" spans="1:7" ht="28.3" x14ac:dyDescent="0.35">
-      <c r="A19" s="6">
+      <c r="A19" s="5">
         <v>18</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3" t="s">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="6" t="s">
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="G19" s="6"/>
+      <c r="G19" s="5"/>
     </row>
     <row r="20" spans="1:7" ht="28.3" x14ac:dyDescent="0.35">
-      <c r="A20" s="7">
+      <c r="A20" s="5">
         <v>19</v>
       </c>
       <c r="B20" s="2"/>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="6">
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="5">
         <v>9</v>
       </c>
-      <c r="G20" s="6"/>
+      <c r="G20" s="5"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21" s="6">
+      <c r="A21" s="5">
         <v>20</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3" t="s">
+      <c r="B21" s="2"/>
+      <c r="C21" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="6">
-        <v>10</v>
-      </c>
-      <c r="G21" s="6"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="5">
+        <v>10</v>
+      </c>
+      <c r="G21" s="5"/>
     </row>
     <row r="22" spans="1:7" ht="28.3" x14ac:dyDescent="0.35">
-      <c r="A22" s="7">
+      <c r="A22" s="5">
         <v>21</v>
       </c>
       <c r="B22" s="2"/>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="6">
-        <v>10</v>
-      </c>
-      <c r="G22" s="6"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="5">
+        <v>10</v>
+      </c>
+      <c r="G22" s="5"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A23" s="7">
+      <c r="A23" s="5">
         <v>22</v>
       </c>
       <c r="B23" s="2"/>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="6">
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="5">
         <v>7.75</v>
       </c>
-      <c r="G23" s="6"/>
+      <c r="G23" s="5"/>
     </row>
     <row r="24" spans="1:7" ht="28.3" x14ac:dyDescent="0.35">
-      <c r="A24" s="6">
+      <c r="A24" s="5">
         <v>22.5</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3" t="s">
+      <c r="B24" s="2"/>
+      <c r="C24" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A25" s="7">
+      <c r="A25" s="5">
         <v>23</v>
       </c>
       <c r="B25" s="2"/>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6">
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5">
         <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A26" s="6">
+      <c r="A26" s="5">
         <v>24</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3" t="s">
+      <c r="B26" s="2"/>
+      <c r="C26" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="6">
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="5">
         <v>8</v>
       </c>
-      <c r="G26" s="6"/>
+      <c r="G26" s="5"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A27" s="6">
+      <c r="A27" s="5">
         <v>25</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3" t="s">
+      <c r="B27" s="2"/>
+      <c r="C27" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="6">
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="5">
         <v>0</v>
       </c>
-      <c r="G27" s="6"/>
+      <c r="G27" s="5"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A28" s="6">
+      <c r="A28" s="5">
         <v>26</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3" t="s">
+      <c r="B28" s="2"/>
+      <c r="C28" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6">
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5">
         <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="28.3" x14ac:dyDescent="0.35">
-      <c r="A29" s="6">
+      <c r="A29" s="5">
         <v>27</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3" t="s">
+      <c r="B29" s="2"/>
+      <c r="C29" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="6">
-        <v>10</v>
-      </c>
-      <c r="G29" s="6"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="5">
+        <v>10</v>
+      </c>
+      <c r="G29" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
